--- a/output/PL_TVM_2026-02.xlsx
+++ b/output/PL_TVM_2026-02.xlsx
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -2193,7 +2193,11 @@
       <c r="A41" t="n">
         <v>1203</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>WROC-GL</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="n">
         <v>0</v>
       </c>
@@ -2232,7 +2236,11 @@
       <c r="A42" t="n">
         <v>1204</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>WROC-GL</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="n">
         <v>0</v>
       </c>
@@ -2271,7 +2279,11 @@
       <c r="A43" t="n">
         <v>1205</v>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>WROCLAW</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="n">
         <v>0</v>
       </c>
@@ -2310,7 +2322,11 @@
       <c r="A44" t="n">
         <v>1206</v>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>WROC-GL</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="n">
         <v>0</v>
       </c>
@@ -2349,7 +2365,11 @@
       <c r="A45" t="n">
         <v>1207</v>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>WROC-GL</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="n">
         <v>0</v>
       </c>
@@ -2388,7 +2408,11 @@
       <c r="A46" t="n">
         <v>1208</v>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>WROC-GL</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="n">
         <v>0</v>
       </c>
@@ -2427,7 +2451,11 @@
       <c r="A47" t="n">
         <v>1210</v>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>WROC-GL</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="n">
         <v>0</v>
       </c>
@@ -2466,7 +2494,11 @@
       <c r="A48" t="n">
         <v>1211</v>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Lubin</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="n">
         <v>0</v>
       </c>
@@ -2505,7 +2537,11 @@
       <c r="A49" t="n">
         <v>1212</v>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>WALBR-M</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="n">
         <v>0</v>
       </c>
@@ -2544,7 +2580,11 @@
       <c r="A50" t="n">
         <v>1213</v>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GLOGOW</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="n">
         <v>0</v>
       </c>
@@ -2583,7 +2623,11 @@
       <c r="A51" t="n">
         <v>1214</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>KRA-BA</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="n">
         <v>0</v>
       </c>
@@ -2622,7 +2666,11 @@
       <c r="A52" t="n">
         <v>1215</v>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>KRA-BA</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="n">
         <v>0</v>
       </c>
@@ -2661,7 +2709,11 @@
       <c r="A53" t="n">
         <v>1217</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1217: Katowice</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="n">
         <v>0</v>
       </c>
@@ -2700,7 +2752,11 @@
       <c r="A54" t="n">
         <v>1219</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KOSZALI</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="n">
         <v>0</v>
       </c>
@@ -2739,7 +2795,11 @@
       <c r="A55" t="n">
         <v>1220</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KROTOSZ</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="n">
         <v>0</v>
       </c>
@@ -2778,7 +2838,11 @@
       <c r="A56" t="n">
         <v>1221</v>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SWID-MI</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="n">
         <v>0</v>
       </c>
@@ -2817,7 +2881,11 @@
       <c r="A57" t="n">
         <v>1222</v>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KOŚCIE</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="n">
         <v>0</v>
       </c>
@@ -2856,7 +2924,11 @@
       <c r="A58" t="n">
         <v>1223</v>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>B-B-GL</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="n">
         <v>0</v>
       </c>
@@ -2895,7 +2967,11 @@
       <c r="A59" t="n">
         <v>1224</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kuźnica</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="n">
         <v>0</v>
       </c>
@@ -2934,7 +3010,11 @@
       <c r="A60" t="n">
         <v>1225</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>STARG</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="n">
         <v>0</v>
       </c>
@@ -2973,7 +3053,11 @@
       <c r="A61" t="n">
         <v>1226</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TARNO</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="n">
         <v>0</v>
       </c>
@@ -3012,7 +3096,11 @@
       <c r="A62" t="n">
         <v>1230</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GLIWICE</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="n">
         <v>0</v>
       </c>
@@ -3051,7 +3139,11 @@
       <c r="A63" t="n">
         <v>1232</v>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>OLAWZA</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="n">
         <v>0</v>
       </c>
@@ -3090,7 +3182,11 @@
       <c r="A64" t="n">
         <v>1234</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ZAGAN</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="n">
         <v>0</v>
       </c>
@@ -3129,7 +3225,11 @@
       <c r="A65" t="n">
         <v>1235</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="n">
         <v>0</v>
       </c>
@@ -3168,7 +3268,11 @@
       <c r="A66" t="n">
         <v>1236</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PELPLIN</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="n">
         <v>0</v>
       </c>
@@ -3207,7 +3311,11 @@
       <c r="A67" t="n">
         <v>1237</v>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="n">
         <v>0</v>
       </c>
@@ -3246,7 +3354,11 @@
       <c r="A68" t="n">
         <v>1238</v>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="n">
         <v>0</v>
       </c>
@@ -3285,7 +3397,11 @@
       <c r="A69" t="n">
         <v>1239</v>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="n">
         <v>0</v>
       </c>
@@ -3324,7 +3440,11 @@
       <c r="A70" t="n">
         <v>1240</v>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="n">
         <v>0</v>
       </c>
@@ -3363,7 +3483,11 @@
       <c r="A71" t="n">
         <v>1241</v>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KONIN</t>
+        </is>
+      </c>
       <c r="C71" s="2" t="n">
         <v>0</v>
       </c>
@@ -3402,7 +3526,11 @@
       <c r="A72" t="n">
         <v>1242</v>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KONIN</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="n">
         <v>0</v>
       </c>
@@ -3441,7 +3569,11 @@
       <c r="A73" t="n">
         <v>1243</v>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GNIEZNO</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="n">
         <v>0</v>
       </c>
@@ -3480,7 +3612,11 @@
       <c r="A74" t="n">
         <v>1244</v>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GNIEZNO</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="n">
         <v>0</v>
       </c>
@@ -3519,7 +3655,11 @@
       <c r="A75" t="n">
         <v>1245</v>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GDA-OLI</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="n">
         <v>0</v>
       </c>
@@ -3558,7 +3698,11 @@
       <c r="A76" t="n">
         <v>1246</v>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OSTROW</t>
+        </is>
+      </c>
       <c r="C76" s="2" t="n">
         <v>0</v>
       </c>
@@ -3599,7 +3743,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Torun: ul. Kujawska 1</t>
+          <t>TOR-GL</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -3640,7 +3784,11 @@
       <c r="A78" t="n">
         <v>1249</v>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>WLOC-ZA</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="n">
         <v>0</v>
       </c>
@@ -3679,7 +3827,11 @@
       <c r="A79" t="n">
         <v>1250</v>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KARPACZ</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="n">
         <v>0</v>
       </c>
@@ -3718,7 +3870,11 @@
       <c r="A80" t="n">
         <v>1252</v>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OPOLE</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="n">
         <v>0</v>
       </c>
@@ -3757,7 +3913,11 @@
       <c r="A81" t="n">
         <v>1254</v>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>WROC-MI</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="n">
         <v>0</v>
       </c>
@@ -3796,7 +3956,11 @@
       <c r="A82" t="n">
         <v>1256</v>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="n">
         <v>0</v>
       </c>
@@ -3835,7 +3999,11 @@
       <c r="A83" t="n">
         <v>1257</v>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="n">
         <v>0</v>
       </c>
@@ -3874,7 +4042,11 @@
       <c r="A84" t="n">
         <v>1259</v>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CZEMPIN</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="n">
         <v>0</v>
       </c>
@@ -3913,7 +4085,11 @@
       <c r="A85" t="n">
         <v>1261</v>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>KRAK-GN</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="n">
         <v>0</v>
       </c>
@@ -3952,7 +4128,11 @@
       <c r="A86" t="n">
         <v>1262</v>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KRAK-GN</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="n">
         <v>0</v>
       </c>
@@ -3991,7 +4171,11 @@
       <c r="A87" t="n">
         <v>1263</v>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KRAK-GN</t>
+        </is>
+      </c>
       <c r="C87" s="2" t="n">
         <v>0</v>
       </c>
@@ -4030,7 +4214,11 @@
       <c r="A88" t="n">
         <v>1264</v>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GORZ-WL</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="n">
         <v>0</v>
       </c>
@@ -4069,7 +4257,11 @@
       <c r="A89" t="n">
         <v>1265</v>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ZIELONA</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="n">
         <v>0</v>
       </c>
@@ -4108,7 +4300,11 @@
       <c r="A90" t="n">
         <v>1266</v>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LESZNO</t>
+        </is>
+      </c>
       <c r="C90" s="2" t="n">
         <v>0</v>
       </c>
@@ -4147,7 +4343,11 @@
       <c r="A91" t="n">
         <v>1267</v>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C91" s="2" t="n">
         <v>0</v>
       </c>
@@ -4186,7 +4386,11 @@
       <c r="A92" t="n">
         <v>1268</v>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="n">
         <v>0</v>
       </c>
@@ -4225,7 +4429,11 @@
       <c r="A93" t="n">
         <v>1269</v>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GDA-GL</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="n">
         <v>0</v>
       </c>
@@ -4264,7 +4472,11 @@
       <c r="A94" t="n">
         <v>1270</v>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Olsztyn</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="n">
         <v>0</v>
       </c>
@@ -4305,7 +4517,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BYDG-GL</t>
+          <t>Bydgoszcz: ul. Zygmunta Augusta 7</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -4346,7 +4558,11 @@
       <c r="A96" t="n">
         <v>1272</v>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>INOWROC</t>
+        </is>
+      </c>
       <c r="C96" s="2" t="n">
         <v>0</v>
       </c>
@@ -4385,7 +4601,11 @@
       <c r="A97" t="n">
         <v>1273</v>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C97" s="2" t="n">
         <v>0</v>
       </c>
@@ -4424,7 +4644,11 @@
       <c r="A98" t="n">
         <v>1274</v>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="n">
         <v>0</v>
       </c>
@@ -4463,7 +4687,11 @@
       <c r="A99" t="n">
         <v>1275</v>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>POZN-D</t>
+        </is>
+      </c>
       <c r="C99" s="2" t="n">
         <v>0</v>
       </c>
@@ -4502,7 +4730,11 @@
       <c r="A100" t="n">
         <v>1276</v>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GDA-STR</t>
+        </is>
+      </c>
       <c r="C100" s="2" t="n">
         <v>0</v>
       </c>
@@ -4541,7 +4773,11 @@
       <c r="A101" t="n">
         <v>1277</v>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GDY-GL</t>
+        </is>
+      </c>
       <c r="C101" s="2" t="n">
         <v>0</v>
       </c>
@@ -4580,7 +4816,11 @@
       <c r="A102" t="n">
         <v>1278</v>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GDY-GL</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="n">
         <v>0</v>
       </c>
@@ -4619,7 +4859,11 @@
       <c r="A103" t="n">
         <v>1279</v>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GDA-GL</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="n">
         <v>0</v>
       </c>
@@ -4658,7 +4902,11 @@
       <c r="A104" t="n">
         <v>1280</v>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GRODZW</t>
+        </is>
+      </c>
       <c r="C104" s="2" t="n">
         <v>0</v>
       </c>
@@ -4697,7 +4945,11 @@
       <c r="A105" t="n">
         <v>1281</v>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GRANOW</t>
+        </is>
+      </c>
       <c r="C105" s="2" t="n">
         <v>0</v>
       </c>
@@ -4736,7 +4988,11 @@
       <c r="A106" t="n">
         <v>1282</v>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>STESZEW</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="n">
         <v>0</v>
       </c>
@@ -4775,7 +5031,11 @@
       <c r="A107" t="n">
         <v>1283</v>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CZERWO</t>
+        </is>
+      </c>
       <c r="C107" s="2" t="n">
         <v>0</v>
       </c>
@@ -4814,7 +5074,11 @@
       <c r="A108" t="n">
         <v>1284</v>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>OWINSK</t>
+        </is>
+      </c>
       <c r="C108" s="2" t="n">
         <v>0</v>
       </c>
@@ -4853,7 +5117,11 @@
       <c r="A109" t="n">
         <v>1285</v>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ZIELWZG</t>
+        </is>
+      </c>
       <c r="C109" s="2" t="n">
         <v>0</v>
       </c>
@@ -4892,7 +5160,11 @@
       <c r="A110" t="n">
         <v>1286</v>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C110" s="2" t="n">
         <v>0</v>
       </c>
@@ -4931,7 +5203,11 @@
       <c r="A111" t="n">
         <v>1287</v>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>KWIDZYN</t>
+        </is>
+      </c>
       <c r="C111" s="2" t="n">
         <v>0</v>
       </c>
@@ -4970,7 +5246,11 @@
       <c r="A112" t="n">
         <v>1288</v>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JASTARN</t>
+        </is>
+      </c>
       <c r="C112" s="2" t="n">
         <v>0</v>
       </c>
@@ -5009,7 +5289,11 @@
       <c r="A113" t="n">
         <v>1289</v>
       </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HEL</t>
+        </is>
+      </c>
       <c r="C113" s="2" t="n">
         <v>0</v>
       </c>
@@ -5048,7 +5332,11 @@
       <c r="A114" t="n">
         <v>1290</v>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SZCZEC</t>
+        </is>
+      </c>
       <c r="C114" s="2" t="n">
         <v>0</v>
       </c>
@@ -5087,7 +5375,11 @@
       <c r="A115" t="n">
         <v>1291</v>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C115" s="2" t="n">
         <v>0</v>
       </c>
@@ -5126,7 +5418,11 @@
       <c r="A116" t="n">
         <v>1292</v>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C116" s="2" t="n">
         <v>0</v>
       </c>
@@ -5165,7 +5461,11 @@
       <c r="A117" t="n">
         <v>1293</v>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C117" s="2" t="n">
         <v>0</v>
       </c>
@@ -5204,7 +5504,11 @@
       <c r="A118" t="n">
         <v>1294</v>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BRZEG</t>
+        </is>
+      </c>
       <c r="C118" s="2" t="n">
         <v>0</v>
       </c>
@@ -5243,7 +5547,11 @@
       <c r="A119" t="n">
         <v>1295</v>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PILA-GL</t>
+        </is>
+      </c>
       <c r="C119" s="2" t="n">
         <v>0</v>
       </c>
@@ -5282,7 +5590,11 @@
       <c r="A120" t="n">
         <v>1296</v>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C120" s="2" t="n">
         <v>0</v>
       </c>
@@ -5321,7 +5633,11 @@
       <c r="A121" t="n">
         <v>1297</v>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>POZN-GL</t>
+        </is>
+      </c>
       <c r="C121" s="2" t="n">
         <v>0</v>
       </c>
@@ -5360,7 +5676,11 @@
       <c r="A122" t="n">
         <v>1298</v>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SZCZEC</t>
+        </is>
+      </c>
       <c r="C122" s="2" t="n">
         <v>0</v>
       </c>
@@ -5399,7 +5719,11 @@
       <c r="A123" t="n">
         <v>1299</v>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>KRAK-GL</t>
+        </is>
+      </c>
       <c r="C123" s="2" t="n">
         <v>0</v>
       </c>
